--- a/output/StructureDefinition-fhir-course-patient01.xlsx
+++ b/output/StructureDefinition-fhir-course-patient01.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T18:59:27+03:00</t>
+    <t>2026-03-22T11:14:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-fhir-course-patient01.xlsx
+++ b/output/StructureDefinition-fhir-course-patient01.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-22T11:14:06+05:30</t>
+    <t>2026-03-22T13:21:26+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-fhir-course-patient01.xlsx
+++ b/output/StructureDefinition-fhir-course-patient01.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5456" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5456" uniqueCount="787">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-22T13:21:26+05:30</t>
+    <t>2026-03-25T09:53:08+03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -880,6 +880,9 @@
 middle name</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>Given names (not always 'first'). Includes middle names</t>
   </si>
   <si>
@@ -1711,9 +1714,6 @@
     <t>Patient.contact.relationship.coding</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Coding
 </t>
   </si>
@@ -2213,9 +2213,6 @@
   </si>
   <si>
     <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
-  </si>
-  <si>
-    <t>Practitioner/456789</t>
   </si>
   <si>
     <t>Reference.reference</t>
@@ -5985,7 +5982,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>91</v>
+        <v>278</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>82</v>
@@ -6003,13 +6000,13 @@
         <v>166</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -6059,7 +6056,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -6074,7 +6071,7 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>83</v>
@@ -6083,7 +6080,7 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>83</v>
@@ -6091,10 +6088,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6120,10 +6117,10 @@
         <v>166</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -6174,7 +6171,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -6189,7 +6186,7 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>83</v>
@@ -6198,7 +6195,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -6206,10 +6203,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6235,10 +6232,10 @@
         <v>166</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6289,7 +6286,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -6304,7 +6301,7 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>83</v>
@@ -6313,7 +6310,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -6321,10 +6318,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6350,14 +6347,14 @@
         <v>216</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -6406,7 +6403,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6421,7 +6418,7 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>83</v>
@@ -6430,7 +6427,7 @@
         <v>83</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -6438,10 +6435,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6464,19 +6461,19 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -6513,10 +6510,10 @@
         <v>83</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>83</v>
@@ -6525,7 +6522,7 @@
         <v>140</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6540,16 +6537,16 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6557,10 +6554,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6672,10 +6669,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6789,10 +6786,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6818,10 +6815,10 @@
         <v>111</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6851,10 +6848,10 @@
         <v>181</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
@@ -6872,7 +6869,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6881,13 +6878,13 @@
         <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>83</v>
@@ -6896,7 +6893,7 @@
         <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6904,10 +6901,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6933,16 +6930,16 @@
         <v>166</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6991,7 +6988,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -7006,7 +7003,7 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>83</v>
@@ -7015,7 +7012,7 @@
         <v>83</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -7023,10 +7020,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7052,16 +7049,16 @@
         <v>111</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -7089,10 +7086,10 @@
         <v>181</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -7110,7 +7107,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -7134,7 +7131,7 @@
         <v>83</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -7142,10 +7139,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7168,16 +7165,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7227,7 +7224,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7259,10 +7256,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7288,10 +7285,10 @@
         <v>216</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7342,7 +7339,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7357,7 +7354,7 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>83</v>
@@ -7374,13 +7371,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -7402,19 +7399,19 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -7463,7 +7460,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7478,16 +7475,16 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
@@ -7495,10 +7492,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7610,10 +7607,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7727,10 +7724,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7756,10 +7753,10 @@
         <v>111</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7771,7 +7768,7 @@
         <v>83</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>83</v>
@@ -7789,10 +7786,10 @@
         <v>181</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>83</v>
@@ -7810,7 +7807,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7819,13 +7816,13 @@
         <v>91</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
@@ -7834,7 +7831,7 @@
         <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7842,10 +7839,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7871,16 +7868,16 @@
         <v>166</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7929,7 +7926,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7944,7 +7941,7 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
@@ -7953,7 +7950,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7961,10 +7958,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7990,16 +7987,16 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -8009,7 +8006,7 @@
         <v>83</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>83</v>
@@ -8027,10 +8024,10 @@
         <v>181</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>83</v>
@@ -8048,7 +8045,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -8072,7 +8069,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -8080,10 +8077,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8106,16 +8103,16 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8165,7 +8162,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -8197,10 +8194,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8226,10 +8223,10 @@
         <v>216</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8280,7 +8277,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8295,7 +8292,7 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>83</v>
@@ -8312,10 +8309,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8341,16 +8338,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8378,10 +8375,10 @@
         <v>181</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -8399,7 +8396,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8414,16 +8411,16 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8431,10 +8428,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8457,19 +8454,19 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8518,7 +8515,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8533,27 +8530,27 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8576,19 +8573,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8637,7 +8634,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8652,7 +8649,7 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>170</v>
@@ -8661,7 +8658,7 @@
         <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8669,10 +8666,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8695,19 +8692,19 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8756,7 +8753,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8771,16 +8768,16 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8788,10 +8785,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8903,10 +8900,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9020,10 +9017,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9049,16 +9046,16 @@
         <v>111</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -9068,10 +9065,10 @@
         <v>83</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>83</v>
@@ -9086,10 +9083,10 @@
         <v>181</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>83</v>
@@ -9107,7 +9104,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -9131,7 +9128,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -9139,10 +9136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9168,13 +9165,13 @@
         <v>111</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9188,7 +9185,7 @@
         <v>83</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>83</v>
@@ -9203,10 +9200,10 @@
         <v>181</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>83</v>
@@ -9224,7 +9221,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9248,7 +9245,7 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -9256,10 +9253,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9285,13 +9282,13 @@
         <v>166</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>264</v>
@@ -9307,7 +9304,7 @@
         <v>83</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>83</v>
@@ -9343,7 +9340,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9367,7 +9364,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -9375,10 +9372,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9389,7 +9386,7 @@
         <v>91</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>83</v>
@@ -9404,10 +9401,10 @@
         <v>166</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9422,7 +9419,7 @@
         <v>83</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>83</v>
@@ -9458,7 +9455,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9473,7 +9470,7 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>83</v>
@@ -9482,7 +9479,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -9490,10 +9487,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9519,10 +9516,10 @@
         <v>166</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9605,10 +9602,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9718,13 +9715,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="B60" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="C60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>83</v>
@@ -9746,13 +9743,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L60" t="s" s="2">
-        <v>441</v>
-      </c>
       <c r="M60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9818,7 +9815,7 @@
         <v>142</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>83</v>
@@ -9835,10 +9832,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9864,10 +9861,10 @@
         <v>166</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9891,7 +9888,7 @@
         <v>83</v>
       </c>
       <c r="W61" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="X61" t="s" s="2">
         <v>83</v>
@@ -9918,7 +9915,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9950,14 +9947,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9979,10 +9976,10 @@
         <v>166</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9997,7 +9994,7 @@
         <v>83</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="U62" t="s" s="2">
         <v>83</v>
@@ -10033,7 +10030,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -10048,7 +10045,7 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>83</v>
@@ -10057,7 +10054,7 @@
         <v>83</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -10065,14 +10062,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -10094,13 +10091,13 @@
         <v>166</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10114,7 +10111,7 @@
         <v>83</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>83</v>
@@ -10150,7 +10147,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10165,7 +10162,7 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>83</v>
@@ -10174,7 +10171,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -10182,14 +10179,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10211,10 +10208,10 @@
         <v>166</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10265,7 +10262,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10280,7 +10277,7 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>83</v>
@@ -10289,7 +10286,7 @@
         <v>83</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -10297,14 +10294,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10326,10 +10323,10 @@
         <v>166</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10344,7 +10341,7 @@
         <v>83</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>83</v>
@@ -10380,7 +10377,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10395,7 +10392,7 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>83</v>
@@ -10404,7 +10401,7 @@
         <v>83</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -10412,10 +10409,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10441,13 +10438,13 @@
         <v>166</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10497,7 +10494,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10512,7 +10509,7 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
@@ -10521,7 +10518,7 @@
         <v>83</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10529,10 +10526,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10558,14 +10555,14 @@
         <v>216</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10578,7 +10575,7 @@
         <v>83</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>83</v>
@@ -10614,7 +10611,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10629,7 +10626,7 @@
         <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
@@ -10638,7 +10635,7 @@
         <v>83</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10646,10 +10643,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10675,14 +10672,14 @@
         <v>187</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10710,10 +10707,10 @@
         <v>192</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
@@ -10731,7 +10728,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10746,16 +10743,16 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10763,10 +10760,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10789,19 +10786,19 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10850,7 +10847,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10865,7 +10862,7 @@
         <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>170</v>
@@ -10874,7 +10871,7 @@
         <v>83</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10882,10 +10879,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10908,19 +10905,19 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10969,7 +10966,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10984,7 +10981,7 @@
         <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>170</v>
@@ -10993,7 +10990,7 @@
         <v>83</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
@@ -11001,10 +10998,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11027,19 +11024,19 @@
         <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -11088,7 +11085,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11100,10 +11097,10 @@
         <v>83</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>170</v>
@@ -11120,10 +11117,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11235,10 +11232,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11352,14 +11349,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11381,10 +11378,10 @@
         <v>136</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>153</v>
@@ -11439,7 +11436,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11471,10 +11468,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11500,14 +11497,14 @@
         <v>187</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11535,10 +11532,10 @@
         <v>192</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11556,7 +11553,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11571,7 +11568,7 @@
         <v>103</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>170</v>
@@ -11580,7 +11577,7 @@
         <v>83</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11588,10 +11585,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11703,10 +11700,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11820,10 +11817,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11831,10 +11828,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>547</v>
+        <v>278</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>547</v>
+        <v>278</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>83</v>
@@ -11940,7 +11937,7 @@
         <v>558</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C79" t="s" s="2">
         <v>559</v>
@@ -12882,7 +12879,7 @@
         <v>608</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C87" t="s" s="2">
         <v>609</v>
@@ -14673,13 +14670,13 @@
         <v>166</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14729,7 +14726,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14744,7 +14741,7 @@
         <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>83</v>
@@ -14753,7 +14750,7 @@
         <v>83</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14790,10 +14787,10 @@
         <v>166</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14844,7 +14841,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14859,7 +14856,7 @@
         <v>103</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>83</v>
@@ -14868,7 +14865,7 @@
         <v>83</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14905,10 +14902,10 @@
         <v>166</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14959,7 +14956,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14974,7 +14971,7 @@
         <v>103</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>83</v>
@@ -14983,7 +14980,7 @@
         <v>83</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -15020,14 +15017,14 @@
         <v>216</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
@@ -15076,7 +15073,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15091,7 +15088,7 @@
         <v>103</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>83</v>
@@ -15100,7 +15097,7 @@
         <v>83</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
@@ -15134,7 +15131,7 @@
         <v>83</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L106" t="s" s="2">
         <v>641</v>
@@ -15146,7 +15143,7 @@
         <v>643</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -15210,7 +15207,7 @@
         <v>103</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>170</v>
@@ -15253,7 +15250,7 @@
         <v>83</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L107" t="s" s="2">
         <v>646</v>
@@ -15327,7 +15324,7 @@
         <v>103</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>170</v>
@@ -15373,7 +15370,7 @@
         <v>111</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M108" t="s" s="2">
         <v>651</v>
@@ -15408,10 +15405,10 @@
         <v>181</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>83</v>
@@ -15444,7 +15441,7 @@
         <v>103</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>170</v>
@@ -15719,7 +15716,7 @@
         <v>83</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L111" t="s" s="2">
         <v>666</v>
@@ -16051,7 +16048,7 @@
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -16073,10 +16070,10 @@
         <v>136</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>153</v>
@@ -16131,7 +16128,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16412,10 +16409,10 @@
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>547</v>
+        <v>278</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>547</v>
+        <v>278</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>83</v>
@@ -16913,55 +16910,55 @@
         <v>83</v>
       </c>
       <c r="S121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF121" t="s" s="2">
         <v>712</v>
       </c>
-      <c r="T121" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF121" t="s" s="2">
+      <c r="AG121" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI121" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>103</v>
@@ -16984,10 +16981,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="B122" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>716</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17013,13 +17010,13 @@
         <v>105</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -17048,28 +17045,28 @@
         <v>192</v>
       </c>
       <c r="Y122" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="Z122" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="Z122" t="s" s="2">
+      <c r="AA122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF122" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17101,10 +17098,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>723</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>724</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17130,13 +17127,13 @@
         <v>157</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17186,7 +17183,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17201,7 +17198,7 @@
         <v>103</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>83</v>
@@ -17218,10 +17215,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17247,13 +17244,13 @@
         <v>166</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>732</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>734</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -17303,7 +17300,7 @@
         <v>83</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -17335,13 +17332,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>691</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>692</v>
@@ -17454,7 +17451,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>704</v>
@@ -17569,7 +17566,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>706</v>
@@ -17686,7 +17683,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>708</v>
@@ -17771,16 +17768,16 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI128" t="s" s="2">
         <v>713</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>714</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>103</v>
@@ -17803,10 +17800,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17832,13 +17829,13 @@
         <v>105</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="N129" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -17867,28 +17864,28 @@
         <v>192</v>
       </c>
       <c r="Y129" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="Z129" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="Z129" t="s" s="2">
+      <c r="AA129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF129" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -17920,10 +17917,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17949,13 +17946,13 @@
         <v>157</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="M130" t="s" s="2">
+      <c r="N130" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -18005,7 +18002,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -18020,7 +18017,7 @@
         <v>103</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>83</v>
@@ -18037,10 +18034,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="B131" t="s" s="2">
         <v>743</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>744</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18152,10 +18149,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="B132" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18269,10 +18266,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="B133" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>748</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18388,10 +18385,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="B134" t="s" s="2">
         <v>749</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>750</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18507,10 +18504,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="B135" t="s" s="2">
         <v>751</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>752</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18555,7 +18552,7 @@
         <v>83</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>203</v>
@@ -18626,10 +18623,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="B136" t="s" s="2">
         <v>754</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>755</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18672,7 +18669,7 @@
         <v>83</v>
       </c>
       <c r="S136" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="T136" t="s" s="2">
         <v>211</v>
@@ -18743,10 +18740,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="B137" t="s" s="2">
         <v>757</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>758</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18858,10 +18855,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="B138" t="s" s="2">
         <v>759</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>760</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18975,10 +18972,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19004,13 +19001,13 @@
         <v>166</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>732</v>
       </c>
-      <c r="M139" t="s" s="2">
+      <c r="N139" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>734</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -19060,7 +19057,7 @@
         <v>83</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -19092,10 +19089,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19121,16 +19118,16 @@
         <v>223</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>763</v>
       </c>
-      <c r="M140" t="s" s="2">
+      <c r="N140" t="s" s="2">
         <v>764</v>
       </c>
-      <c r="N140" t="s" s="2">
+      <c r="O140" t="s" s="2">
         <v>765</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>766</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>83</v>
@@ -19179,7 +19176,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -19197,7 +19194,7 @@
         <v>659</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>83</v>
@@ -19211,10 +19208,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19237,19 +19234,19 @@
         <v>92</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>769</v>
       </c>
-      <c r="M141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>770</v>
       </c>
-      <c r="N141" t="s" s="2">
+      <c r="O141" t="s" s="2">
         <v>771</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>772</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>83</v>
@@ -19298,7 +19295,7 @@
         <v>83</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -19313,7 +19310,7 @@
         <v>103</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>170</v>
@@ -19330,10 +19327,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19445,10 +19442,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19562,14 +19559,14 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -19591,10 +19588,10 @@
         <v>136</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>153</v>
@@ -19649,7 +19646,7 @@
         <v>83</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
@@ -19681,10 +19678,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19707,16 +19704,16 @@
         <v>92</v>
       </c>
       <c r="K145" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="L145" t="s" s="2">
         <v>778</v>
       </c>
-      <c r="L145" t="s" s="2">
+      <c r="M145" t="s" s="2">
         <v>779</v>
       </c>
-      <c r="M145" t="s" s="2">
+      <c r="N145" t="s" s="2">
         <v>780</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>781</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -19766,7 +19763,7 @@
         <v>83</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>91</v>
@@ -19790,7 +19787,7 @@
         <v>83</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>83</v>
@@ -19798,10 +19795,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19827,10 +19824,10 @@
         <v>111</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="M146" t="s" s="2">
         <v>784</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>785</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -19860,11 +19857,11 @@
         <v>181</v>
       </c>
       <c r="Y146" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="Z146" t="s" s="2">
         <v>785</v>
       </c>
-      <c r="Z146" t="s" s="2">
-        <v>786</v>
-      </c>
       <c r="AA146" t="s" s="2">
         <v>83</v>
       </c>
@@ -19881,7 +19878,7 @@
         <v>83</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>91</v>
@@ -19896,7 +19893,7 @@
         <v>103</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>170</v>
